--- a/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N45_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5177_W0015F0001T0006Z000C1N45_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.92756493163527</v>
+        <v>5.838229301390731</v>
       </c>
       <c r="D2" t="n">
-        <v>36.4298538630937</v>
+        <v>5.919851252752728</v>
       </c>
       <c r="E2" t="n">
-        <v>9.17207305120955</v>
+        <v>1.490461870821552</v>
       </c>
       <c r="F2" t="n">
-        <v>9.016400258123328</v>
+        <v>1.465165041945041</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.39810874271436</v>
+        <v>5.914692670691085</v>
       </c>
       <c r="D3" t="n">
-        <v>35.81628766611593</v>
+        <v>5.820146745743839</v>
       </c>
       <c r="E3" t="n">
-        <v>9.17207305120955</v>
+        <v>1.490461870821552</v>
       </c>
       <c r="F3" t="n">
-        <v>9.016400258123328</v>
+        <v>1.465165041945041</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>43.93150954476677</v>
+        <v>7.1388703010246</v>
       </c>
       <c r="D4" t="n">
-        <v>44.17891992329996</v>
+        <v>7.179074487536244</v>
       </c>
       <c r="E4" t="n">
-        <v>9.17207305120955</v>
+        <v>1.490461870821552</v>
       </c>
       <c r="F4" t="n">
-        <v>9.016400258123328</v>
+        <v>1.465165041945041</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>46.6090925360466</v>
+        <v>7.573977537107573</v>
       </c>
       <c r="D5" t="n">
-        <v>46.05577968495096</v>
+        <v>7.484064198804532</v>
       </c>
       <c r="E5" t="n">
-        <v>9.17207305120955</v>
+        <v>1.490461870821552</v>
       </c>
       <c r="F5" t="n">
-        <v>9.016400258123328</v>
+        <v>1.465165041945041</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>44.56173940342905</v>
+        <v>7.241282653057221</v>
       </c>
       <c r="D6" t="n">
-        <v>44.07175150557354</v>
+        <v>7.1616596196557</v>
       </c>
       <c r="E6" t="n">
-        <v>9.17207305120955</v>
+        <v>1.490461870821552</v>
       </c>
       <c r="F6" t="n">
-        <v>9.016400258123328</v>
+        <v>1.465165041945041</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>38.75951034020614</v>
+        <v>6.298420430283498</v>
       </c>
       <c r="D7" t="n">
-        <v>38.79353619414178</v>
+        <v>6.303949631548039</v>
       </c>
       <c r="E7" t="n">
-        <v>9.17207305120955</v>
+        <v>1.490461870821552</v>
       </c>
       <c r="F7" t="n">
-        <v>9.016400258123328</v>
+        <v>1.465165041945041</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>48.61879454596175</v>
+        <v>7.900554113718784</v>
       </c>
       <c r="D8" t="n">
-        <v>48.25812458164733</v>
+        <v>7.841945244517691</v>
       </c>
       <c r="E8" t="n">
-        <v>9.17207305120955</v>
+        <v>1.490461870821552</v>
       </c>
       <c r="F8" t="n">
-        <v>9.016400258123328</v>
+        <v>1.465165041945041</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>33.82731827580149</v>
+        <v>5.496939219817742</v>
       </c>
       <c r="D9" t="n">
-        <v>33.87711629400848</v>
+        <v>5.505031397776379</v>
       </c>
       <c r="E9" t="n">
-        <v>9.17207305120955</v>
+        <v>1.490461870821552</v>
       </c>
       <c r="F9" t="n">
-        <v>9.016400258123328</v>
+        <v>1.465165041945041</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>23.68134859919168</v>
+        <v>3.848219147368647</v>
       </c>
       <c r="D10" t="n">
-        <v>23.70859040045627</v>
+        <v>3.852645940074143</v>
       </c>
       <c r="E10" t="n">
-        <v>9.17207305120955</v>
+        <v>1.490461870821552</v>
       </c>
       <c r="F10" t="n">
-        <v>9.016400258123328</v>
+        <v>1.465165041945041</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>17.0914808566906</v>
+        <v>2.777365639212222</v>
       </c>
       <c r="D11" t="n">
-        <v>17.61263883648359</v>
+        <v>2.862053810928584</v>
       </c>
       <c r="E11" t="n">
-        <v>9.17207305120955</v>
+        <v>1.490461870821552</v>
       </c>
       <c r="F11" t="n">
-        <v>9.016400258123328</v>
+        <v>1.465165041945041</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>23.63028097073449</v>
+        <v>3.839920657744354</v>
       </c>
       <c r="D12" t="n">
-        <v>23.88711591674793</v>
+        <v>3.881656336471539</v>
       </c>
       <c r="E12" t="n">
-        <v>9.17207305120955</v>
+        <v>1.490461870821552</v>
       </c>
       <c r="F12" t="n">
-        <v>9.016400258123328</v>
+        <v>1.465165041945041</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>42.40216854985999</v>
+        <v>6.890352389352249</v>
       </c>
       <c r="D13" t="n">
-        <v>42.92200374144245</v>
+        <v>6.974825607984398</v>
       </c>
       <c r="E13" t="n">
-        <v>9.17207305120955</v>
+        <v>1.490461870821552</v>
       </c>
       <c r="F13" t="n">
-        <v>9.016400258123328</v>
+        <v>1.465165041945041</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>39.26428934445205</v>
+        <v>6.380447018473459</v>
       </c>
       <c r="D14" t="n">
-        <v>39.61147335775755</v>
+        <v>6.436864420635602</v>
       </c>
       <c r="E14" t="n">
-        <v>9.17207305120955</v>
+        <v>1.490461870821552</v>
       </c>
       <c r="F14" t="n">
-        <v>9.016400258123328</v>
+        <v>1.465165041945041</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>43.61496716220788</v>
+        <v>7.087432163858781</v>
       </c>
       <c r="D15" t="n">
-        <v>43.84504609228432</v>
+        <v>7.124819989996202</v>
       </c>
       <c r="E15" t="n">
-        <v>9.17207305120955</v>
+        <v>1.490461870821552</v>
       </c>
       <c r="F15" t="n">
-        <v>9.016400258123328</v>
+        <v>1.465165041945041</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
